--- a/artfynd/A 25287-2025 artfynd.xlsx
+++ b/artfynd/A 25287-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,6 +1912,365 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129698788</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>457152</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6678249</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129698808</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>457150</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6678246</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129698671</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Smala Mörtmossen, Smala Mörtmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>457136</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6678326</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 3.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25287-2025 artfynd.xlsx
+++ b/artfynd/A 25287-2025 artfynd.xlsx
@@ -1917,7 +1917,7 @@
         <v>129698788</v>
       </c>
       <c r="B12" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>129698808</v>
       </c>
       <c r="B13" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>129698671</v>
       </c>
       <c r="B14" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 25287-2025 artfynd.xlsx
+++ b/artfynd/A 25287-2025 artfynd.xlsx
@@ -1917,7 +1917,7 @@
         <v>129698788</v>
       </c>
       <c r="B12" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>129698808</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>129698671</v>
       </c>
       <c r="B14" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 25287-2025 artfynd.xlsx
+++ b/artfynd/A 25287-2025 artfynd.xlsx
@@ -1917,7 +1917,7 @@
         <v>129698788</v>
       </c>
       <c r="B12" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>129698808</v>
       </c>
       <c r="B13" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>129698671</v>
       </c>
       <c r="B14" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 25287-2025 artfynd.xlsx
+++ b/artfynd/A 25287-2025 artfynd.xlsx
@@ -1917,7 +1917,7 @@
         <v>129698788</v>
       </c>
       <c r="B12" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>129698671</v>
       </c>
       <c r="B14" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
